--- a/Emisores.xlsx
+++ b/Emisores.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb5bc0792163cb23/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD17EAFF-BE0D-4454-A41D-9BE3111DDD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{BD17EAFF-BE0D-4454-A41D-9BE3111DDD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D261D2D-B2A9-49DC-AFB2-C194E1FE11B4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8DC596D6-89CA-4DB4-A49E-B2DC92DCB696}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8DC596D6-89CA-4DB4-A49E-B2DC92DCB696}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,38 +42,643 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Rutas de Lima</t>
-  </si>
-  <si>
-    <t>Norvial</t>
-  </si>
-  <si>
-    <t>Aenza</t>
-  </si>
-  <si>
-    <t>Cementos Pacasmayo</t>
-  </si>
-  <si>
-    <t>Unacem</t>
-  </si>
-  <si>
-    <t>Kallpa Generación</t>
-  </si>
-  <si>
-    <t>Pluz Energia</t>
-  </si>
-  <si>
-    <t>Auna S.A</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="207">
+  <si>
+    <t>CORPORACION PRIMAX S.A.</t>
+  </si>
+  <si>
+    <t>Santander Consumo Peru S.A.</t>
+  </si>
+  <si>
+    <t>BANCO INTERNACIONAL DEL PERU</t>
+  </si>
+  <si>
+    <t>FONDO MI VIVIENDA S.A.</t>
+  </si>
+  <si>
+    <t>COMPASS GROUP SAFI S.A</t>
+  </si>
+  <si>
+    <t>BANCO DE CREDITO DEL PERU</t>
+  </si>
+  <si>
+    <t>BANCO BBVA PERU</t>
+  </si>
+  <si>
+    <t>BANCO SANTANDER PERÚ</t>
+  </si>
+  <si>
+    <t>BANCO MIBANCO</t>
+  </si>
+  <si>
+    <t>BANCO GNB PERU S.A.</t>
+  </si>
+  <si>
+    <t>BANCO INTERAMERICANO DE FINANZAS</t>
+  </si>
+  <si>
+    <t>SANTANDER CONSUMER BANK (EX CREDISCOTIA)</t>
+  </si>
+  <si>
+    <t>BANCO RIPLEY PERÚ S.A.</t>
+  </si>
+  <si>
+    <t>BANCO BCI PERU</t>
+  </si>
+  <si>
+    <t>COMPARTAMOS BANCO S.A.</t>
+  </si>
+  <si>
+    <t>GOBIERNO PERUANO</t>
+  </si>
+  <si>
+    <t>REPUBLICA FEDERAL DE BRASIL</t>
+  </si>
+  <si>
+    <t>REPUBLICA DE COLOMBIA</t>
+  </si>
+  <si>
+    <t>REPUBLICA DE MEXICO</t>
+  </si>
+  <si>
+    <t>FINANCIERA OH S.A</t>
+  </si>
+  <si>
+    <t>INTERSEGURO COMPAÑIA DE SEGUROS S.A.</t>
+  </si>
+  <si>
+    <t>PACIFICO COMPAÑÍA DE SEGUROS Y REASEGUROS S.A.</t>
+  </si>
+  <si>
+    <t>LUZ DEL SUR S.A.A</t>
+  </si>
+  <si>
+    <t>ALICORP S.A.</t>
+  </si>
+  <si>
+    <t>PLUZ ENERGIA PERU S.A..A (Antes ENDISPC1)</t>
+  </si>
+  <si>
+    <t>VOLCAN CIA MINERA S A</t>
+  </si>
+  <si>
+    <t>ORAZUL ENERGIA PERU SAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED DE ENERGIA DEL PERU SA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGIE ENERGIA PERU S.A. </t>
+  </si>
+  <si>
+    <t>RUTAS DE LIMA S.A.C.</t>
+  </si>
+  <si>
+    <t>NORVIAL S.A.</t>
+  </si>
+  <si>
+    <t>Hunt Oil Company of Peru L.L.C., Sucursal del Perú</t>
+  </si>
+  <si>
+    <t>ELECTRO DUNAS S.A.A</t>
+  </si>
+  <si>
+    <t>CORPORACION FINANCIERA DE DESARROLLO S.A.</t>
+  </si>
+  <si>
+    <t>IFH PERU LTD</t>
+  </si>
+  <si>
+    <t>INRETAIL SHOPPING MALLS</t>
+  </si>
+  <si>
+    <t>INRETAIL CONSUMER</t>
+  </si>
+  <si>
+    <t>RED DORSAL FINANCE LIMITED</t>
+  </si>
+  <si>
+    <t>INTERGROUP</t>
+  </si>
+  <si>
+    <t>UNACEM CORP S.A.A.</t>
+  </si>
+  <si>
+    <t>CREDICORP LTD</t>
+  </si>
+  <si>
+    <t>AENZA S.A.A. (Antes Graña y Montero S.A.A.)</t>
+  </si>
+  <si>
+    <t>ENEL GENERACION PERU S.A.A. (Antes EDEGEL S.A.A.)</t>
+  </si>
+  <si>
+    <t>CEMENTOS PACASMAYO S.A</t>
+  </si>
+  <si>
+    <t>Sociedad Minera Cerro Verde SAA</t>
+  </si>
+  <si>
+    <t>INRETAIL PERU CORP</t>
+  </si>
+  <si>
+    <t>FERREYCORP S.A.A.</t>
+  </si>
+  <si>
+    <t>FOSSAL S.A.A.</t>
+  </si>
+  <si>
+    <t>NEXA RESOURCES PERU S.A.A.</t>
+  </si>
+  <si>
+    <t>INVERSIONES PORTUARIAS CHANCAY S.A.</t>
+  </si>
+  <si>
+    <t>CUMBRA HOLDING S.A.A.</t>
+  </si>
+  <si>
+    <t>ACEROS AREQUIPA S.A</t>
+  </si>
+  <si>
+    <t>MINSUR S.A</t>
+  </si>
+  <si>
+    <t>CIA. DE MINAS BUENAVENTURA S.A.A.</t>
+  </si>
+  <si>
+    <t>HOCHSCHILD MINING (PERU) S.A.</t>
+  </si>
+  <si>
+    <t>Hudbay Minerals inc</t>
+  </si>
+  <si>
+    <t>NEXA RESOURCES S.A. (Limite Local)</t>
+  </si>
+  <si>
+    <t>BD CAPITAL SOCIEDAD ADMINISTRADORA DE FONDOS S.A.C.</t>
+  </si>
+  <si>
+    <t>HMC CAPITAL PERU S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATE STREET BANK </t>
+  </si>
+  <si>
+    <t>AllianceBernstein (Luxemburgo) S.á.r.l</t>
+  </si>
+  <si>
+    <t>UBS Fund Management (Luxembourg) S.A.</t>
+  </si>
+  <si>
+    <t>JPMorgan Asset Management (Europe) S.à.r.l.</t>
+  </si>
+  <si>
+    <t>THE VANGUARD GROUP</t>
+  </si>
+  <si>
+    <t>Schroder Investment Management (Luxembourg) S.A.</t>
+  </si>
+  <si>
+    <t>ABERDEEN INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>Investec Asset Management Luxembourg S.A.</t>
+  </si>
+  <si>
+    <t>GARTMORE INVESTMENT MANAGEMENT PLC</t>
+  </si>
+  <si>
+    <t>DWS Investment S.A.</t>
+  </si>
+  <si>
+    <t>AXA FUNDS MANAGEMENT S.A.</t>
+  </si>
+  <si>
+    <t>BNP Paribas Investment Partners Luxembourg</t>
+  </si>
+  <si>
+    <t>Allianz Global Investors GMBH</t>
+  </si>
+  <si>
+    <t>Vontobel Asset Management S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baring International Fund Managers (Ireland) Limited </t>
+  </si>
+  <si>
+    <t>Moneda S.A. Administradora General de Fondos</t>
+  </si>
+  <si>
+    <t>VAN ECK ASSOCIATES CORPORATION</t>
+  </si>
+  <si>
+    <t>BlackRock Asset Management Ireland</t>
+  </si>
+  <si>
+    <t>FranklinTempleton International Services S.á.r.l</t>
+  </si>
+  <si>
+    <t>Pictet Asset Management (Europe) S.A.</t>
+  </si>
+  <si>
+    <t>Neuberger Berman Asset Management Ireland Limited</t>
+  </si>
+  <si>
+    <t>BLACKROCK FUND ADVISORS</t>
+  </si>
+  <si>
+    <t>WINDOMTREE ASSET MANAGEMENT INC</t>
+  </si>
+  <si>
+    <t>NOMURA ASSET MANAGEMENT U.K.</t>
+  </si>
+  <si>
+    <t>ROBECO LUXEMBOURG S.A.</t>
+  </si>
+  <si>
+    <t>GAM International Management Limited</t>
+  </si>
+  <si>
+    <t>STATE STREET BANK AND TRUS COMPANY</t>
+  </si>
+  <si>
+    <t>Deutsche Asset Management S.A.</t>
+  </si>
+  <si>
+    <t>Amundi Luxembourg SA</t>
+  </si>
+  <si>
+    <t>Wellington Luxembourg S.à r.l. (Wellington Luxembourg)</t>
+  </si>
+  <si>
+    <t>SANTANDER ASSET MANAGEMENT LUXEMBOURG S.A</t>
+  </si>
+  <si>
+    <t>FIRST TRUST  PORTAFOLIOS LP</t>
+  </si>
+  <si>
+    <t>Groupama Asset Management</t>
+  </si>
+  <si>
+    <t>PIMCO Global Advisors (Ireland) Limited</t>
+  </si>
+  <si>
+    <t>Invesco Fund Managers Limited</t>
+  </si>
+  <si>
+    <t>Candriam Luxembourg</t>
+  </si>
+  <si>
+    <t>Veritas Asset Management LLP</t>
+  </si>
+  <si>
+    <t>DEGROOF PETERCAM ASSET SERVICES S.A.</t>
+  </si>
+  <si>
+    <t>Lazard Freres Gestion SAS</t>
+  </si>
+  <si>
+    <t>Jupiter Unit Trust Managers Limited</t>
+  </si>
+  <si>
+    <t>M&amp;G Luxemburgo S.A.</t>
+  </si>
+  <si>
+    <t>KRANE FUNDS ADVISORS, LLC</t>
+  </si>
+  <si>
+    <t>Ashmore Investment Management (Ireland) Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moneda S.A. Administradora </t>
+  </si>
+  <si>
+    <t>Edmond de Rothschild Asset Management (Luxembourg)</t>
+  </si>
+  <si>
+    <t>LARRAINVIAL ASSET MANAGEMENT SICAV</t>
+  </si>
+  <si>
+    <t>BlueBay Funds Management Company S.A.</t>
+  </si>
+  <si>
+    <t>Invesco Capital Management LLC</t>
+  </si>
+  <si>
+    <t>Schroder Investment Management (Europe) SA</t>
+  </si>
+  <si>
+    <t>Joh. Berenberg, Gossler &amp; Co. KG</t>
+  </si>
+  <si>
+    <t>MSIM Fund Management (Ireland) Limited</t>
+  </si>
+  <si>
+    <t>Compass Group Chile S.A. Administradora General de Fondos</t>
+  </si>
+  <si>
+    <t>GLOBAL X MANAGEMENT Co LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP Morgan Investment Management Inc. </t>
+  </si>
+  <si>
+    <t>NS Partners Europe S.A</t>
+  </si>
+  <si>
+    <t>Ninety One Luxembourg SA</t>
+  </si>
+  <si>
+    <t>LionTrust European Dynamic</t>
+  </si>
+  <si>
+    <t>Jupiter Asset Management International S.A.</t>
+  </si>
+  <si>
+    <t>Carne Global Fund Managers (Luxembourg) S.A</t>
+  </si>
+  <si>
+    <t>Carne Global Fund Managers (Ireland) Limited Carne</t>
+  </si>
+  <si>
+    <t>PIMCO ETF Trust</t>
+  </si>
+  <si>
+    <t>AEGON ASSET MANAGEMENT UK PLC plc</t>
+  </si>
+  <si>
+    <t>Lazard Fund Managers (Ireland) Limited </t>
+  </si>
+  <si>
+    <t>ECOPETROL S.A.</t>
+  </si>
+  <si>
+    <t>EMPRESAS PUBLICAS MEDELLIN</t>
+  </si>
+  <si>
+    <t>ROYAL BANK OF CANADA</t>
+  </si>
+  <si>
+    <t>BANCO DE LA NACION</t>
+  </si>
+  <si>
+    <t>KALLPA GENERACION SA</t>
+  </si>
+  <si>
+    <t>GAS NATURAL DE LIMA Y CALLAO S.A.</t>
+  </si>
+  <si>
+    <t>FALABELLA PERU S.A.A. (HOLDING)</t>
+  </si>
+  <si>
+    <t>ADMINISTRADORA JOCKEY PLAZA SHOPPING CENTER SA</t>
+  </si>
+  <si>
+    <t>PACIFICO SALUD EPS S.A.</t>
+  </si>
+  <si>
+    <t>Larraín Vial S.A. Sociedad Administradora de Fondos de Inversión</t>
+  </si>
+  <si>
+    <t>FIDELITY FUNDS</t>
+  </si>
+  <si>
+    <t>Matthews International Capital Management, LLC</t>
+  </si>
+  <si>
+    <t>Invesco Management S.A.</t>
+  </si>
+  <si>
+    <t>GLG Partners LP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackRock Luxembourg S.A. </t>
+  </si>
+  <si>
+    <t>UTI International (Singapore) Private Limited</t>
+  </si>
+  <si>
+    <t>ASF VIII GP Limited</t>
+  </si>
+  <si>
+    <t>MREP-SCIF II GP, L.P.</t>
+  </si>
+  <si>
+    <t>FRO Fund III GP LLC</t>
+  </si>
+  <si>
+    <t>Lexington Partners GP Holdings IX LLC</t>
+  </si>
+  <si>
+    <t>Tishman S European  RE VIII GP S.á.r.l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGSF VI Feeder GP, LLC </t>
+  </si>
+  <si>
+    <t>NB Private Debt Associates III, LP</t>
+  </si>
+  <si>
+    <t>CVC Credit Partners Global Special Situations II S.à R.L.</t>
+  </si>
+  <si>
+    <t>Coller International General Partner VIII, L.P.</t>
+  </si>
+  <si>
+    <t>EQT Infrastructure IV (GP) SCS</t>
+  </si>
+  <si>
+    <t>Cevine Capital Management (VII) Limited Partnership Incorporated</t>
+  </si>
+  <si>
+    <t>Strategic Partners Fund Solutions GP (Offshore) Ltd.</t>
+  </si>
+  <si>
+    <t>Hamilton Lane Global SMID II GP LLC</t>
+  </si>
+  <si>
+    <t>Oaktree Special Situations Fund II GP, L.P.</t>
+  </si>
+  <si>
+    <t>Platinum Equity Partners V, L.P.</t>
+  </si>
+  <si>
+    <t>SPFSA RE VII L.L.C.</t>
+  </si>
+  <si>
+    <t>APAX X USD GP L.P. Inc</t>
+  </si>
+  <si>
+    <t>Bain Capital Distressed and Special Situations 2019 Investors</t>
+  </si>
+  <si>
+    <t>Warburg Pincus Global Growth GP, L.P.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insight Associates XI, L.P. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antin Infrastructure Partners IV Luxembourg </t>
+  </si>
+  <si>
+    <t>Buyout VII Management SAS</t>
+  </si>
+  <si>
+    <t>IK IX Fund GP S.A.R.L.</t>
+  </si>
+  <si>
+    <t>Morgan Stanley Infrastructure III Investors GP S.A.R.L.</t>
+  </si>
+  <si>
+    <t>Francisco Partners GP VI LP</t>
+  </si>
+  <si>
+    <t>Thoma Bravo XIV L.P</t>
+  </si>
+  <si>
+    <t>Partners Group Management II, S.a.r.l.</t>
+  </si>
+  <si>
+    <t>Cortland Enhanced Value Fund V GP, LLCC</t>
+  </si>
+  <si>
+    <t>EQT Infrastructure V (General Partner) S.à.r.l.</t>
+  </si>
+  <si>
+    <t>G Squared Equity GP V S.à.r.l</t>
+  </si>
+  <si>
+    <t>COMPAÑIA MINERA MARCOBRE S.A.C.</t>
+  </si>
+  <si>
+    <t>AUNA S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfraVia European Fund V SCSp </t>
+  </si>
+  <si>
+    <t>Antin Infrastructure Partners V Luxembourg GP, S.A R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knightsbridge Management X LLC </t>
+  </si>
+  <si>
+    <t>Cortland Enhanced Value Fund VI GP, LLC</t>
+  </si>
+  <si>
+    <t>EQT Infrastructure VI (General Partner) S.à.r.l.</t>
+  </si>
+  <si>
+    <t>Platinum Equity Partners VI, L.P.</t>
+  </si>
+  <si>
+    <t>PAI Partners VIII GP S.à r.l.</t>
+  </si>
+  <si>
+    <t>Vitruvian Luxcar GP S.à r.l.</t>
+  </si>
+  <si>
+    <t>Triton Fund 6 General Partner SARL</t>
+  </si>
+  <si>
+    <t>Veritas Capital Partners IX, L.L.C.</t>
+  </si>
+  <si>
+    <t>InfraVia GP VI Sàrl</t>
+  </si>
+  <si>
+    <t>Insight Associates XIII, L.P.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ridgemont Equity Management V, L.P. </t>
+  </si>
+  <si>
+    <t>ICG Europe Fund IX Feeder SCSp</t>
+  </si>
+  <si>
+    <t>CapVest Private Equity VI GP SCSp</t>
+  </si>
+  <si>
+    <t>Partners Group Cayman Management Direct Infra IV Limited</t>
+  </si>
+  <si>
+    <t>EMISOR</t>
+  </si>
+  <si>
+    <t>TIPO_DE_INSTRUMENTO</t>
+  </si>
+  <si>
+    <t>Bonos Empresas Privadas</t>
+  </si>
+  <si>
+    <t>Papeles Comerciales</t>
+  </si>
+  <si>
+    <t>Otros Bonos Sistema Financiero</t>
+  </si>
+  <si>
+    <t>Fondos de Inversion Tradicional Local</t>
+  </si>
+  <si>
+    <t>Depositos a Plazo</t>
+  </si>
+  <si>
+    <t>CD Seriados Subastado Bcos</t>
+  </si>
+  <si>
+    <t>Bonos Gobierno Central de la Republica</t>
+  </si>
+  <si>
+    <t>Tit Deu Emi Estados Extrajero</t>
+  </si>
+  <si>
+    <t>Bonos Subordinados</t>
+  </si>
+  <si>
+    <t>Titulos con Derecho Crediticio</t>
+  </si>
+  <si>
+    <t>Acciones del Capital Social</t>
+  </si>
+  <si>
+    <t>Acciones del Trabajo</t>
+  </si>
+  <si>
+    <t>VRA Empresas Nacionales</t>
+  </si>
+  <si>
+    <t>Fondos Mutuos del Extranjero</t>
+  </si>
+  <si>
+    <t>Tit Deu Emi Empresas Publicas Extranjero</t>
+  </si>
+  <si>
+    <t>Overnight Deposits</t>
+  </si>
+  <si>
+    <t>Fondos de Inversion Alternativos Locales</t>
+  </si>
+  <si>
+    <t>Fondo Mutuos Alterniativos Extranjero</t>
+  </si>
+  <si>
+    <t>Acciones en el Extranjero</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -86,7 +694,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -94,12 +702,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,50 +1060,1650 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBDDDA3-EEF5-4226-BC33-FF54A0B53D64}">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B204"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>148</v>
+      </c>
+      <c r="B53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B62" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>173</v>
+      </c>
+      <c r="B64" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>50</v>
+      </c>
+      <c r="B66" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>122</v>
+      </c>
+      <c r="B71" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>32</v>
+      </c>
+      <c r="B73" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B77" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B78" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>166</v>
+      </c>
+      <c r="B79" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>174</v>
+      </c>
+      <c r="B80" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>46</v>
+      </c>
+      <c r="B82" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>132</v>
+      </c>
+      <c r="B83" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>47</v>
+      </c>
+      <c r="B87" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>47</v>
+      </c>
+      <c r="B88" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>162</v>
+      </c>
+      <c r="B89" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>77</v>
+      </c>
+      <c r="B90" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>167</v>
+      </c>
+      <c r="B92" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>84</v>
+      </c>
+      <c r="B93" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>67</v>
+      </c>
+      <c r="B94" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>127</v>
+      </c>
+      <c r="B95" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>135</v>
+      </c>
+      <c r="B96" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>111</v>
+      </c>
+      <c r="B97" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>91</v>
+      </c>
+      <c r="B99" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>150</v>
+      </c>
+      <c r="B100" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>58</v>
+      </c>
+      <c r="B101" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>54</v>
+      </c>
+      <c r="B102" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>55</v>
+      </c>
+      <c r="B103" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>31</v>
+      </c>
+      <c r="B104" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>34</v>
+      </c>
+      <c r="B106" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>160</v>
+      </c>
+      <c r="B107" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>170</v>
+      </c>
+      <c r="B108" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>180</v>
+      </c>
+      <c r="B109" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>36</v>
+      </c>
+      <c r="B110" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>35</v>
+      </c>
+      <c r="B112" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>157</v>
+      </c>
+      <c r="B113" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>181</v>
+      </c>
+      <c r="B114" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>38</v>
+      </c>
+      <c r="B115" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>20</v>
+      </c>
+      <c r="B116" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>49</v>
+      </c>
+      <c r="B117" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>106</v>
+      </c>
+      <c r="B118" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>93</v>
+      </c>
+      <c r="B119" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>134</v>
+      </c>
+      <c r="B120" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>66</v>
+      </c>
+      <c r="B121" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>108</v>
+      </c>
+      <c r="B122" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>112</v>
+      </c>
+      <c r="B123" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>62</v>
+      </c>
+      <c r="B124" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>116</v>
+      </c>
+      <c r="B125" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>98</v>
+      </c>
+      <c r="B126" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>172</v>
+      </c>
+      <c r="B128" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>100</v>
+      </c>
+      <c r="B129" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>104</v>
+      </c>
+      <c r="B131" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>97</v>
+      </c>
+      <c r="B132" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>121</v>
+      </c>
+      <c r="B133" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>115</v>
+      </c>
+      <c r="B135" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>22</v>
+      </c>
+      <c r="B136" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B137" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>133</v>
+      </c>
+      <c r="B138" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>52</v>
+      </c>
+      <c r="B139" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>52</v>
+      </c>
+      <c r="B140" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>102</v>
+      </c>
+      <c r="B141" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>74</v>
+      </c>
+      <c r="B142" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>161</v>
+      </c>
+      <c r="B143" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>139</v>
+      </c>
+      <c r="B144" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>109</v>
+      </c>
+      <c r="B145" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>144</v>
+      </c>
+      <c r="B146" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>79</v>
+      </c>
+      <c r="B147" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>48</v>
+      </c>
+      <c r="B148" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>56</v>
+      </c>
+      <c r="B149" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>114</v>
+      </c>
+      <c r="B150" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>82</v>
+      </c>
+      <c r="B151" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>30</v>
+      </c>
+      <c r="B152" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>113</v>
+      </c>
+      <c r="B153" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>151</v>
+      </c>
+      <c r="B154" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>26</v>
+      </c>
+      <c r="B155" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>21</v>
+      </c>
+      <c r="B156" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>130</v>
+      </c>
+      <c r="B157" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>176</v>
+      </c>
+      <c r="B158" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>185</v>
+      </c>
+      <c r="B159" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>164</v>
+      </c>
+      <c r="B160" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>143</v>
+      </c>
+      <c r="B161" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>78</v>
+      </c>
+      <c r="B162" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>119</v>
+      </c>
+      <c r="B163" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>92</v>
+      </c>
+      <c r="B164" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>152</v>
+      </c>
+      <c r="B165" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>175</v>
+      </c>
+      <c r="B166" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>24</v>
+      </c>
+      <c r="B167" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>24</v>
+      </c>
+      <c r="B168" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>27</v>
+      </c>
+      <c r="B169" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>37</v>
+      </c>
+      <c r="B170" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>17</v>
+      </c>
+      <c r="B171" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>18</v>
+      </c>
+      <c r="B172" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>16</v>
+      </c>
+      <c r="B173" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>182</v>
+      </c>
+      <c r="B174" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>83</v>
+      </c>
+      <c r="B175" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>124</v>
+      </c>
+      <c r="B176" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>29</v>
+      </c>
+      <c r="B177" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>89</v>
+      </c>
+      <c r="B178" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>11</v>
+      </c>
+      <c r="B179" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
+      <c r="B180" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>107</v>
+      </c>
+      <c r="B181" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>64</v>
+      </c>
+      <c r="B182" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>44</v>
+      </c>
+      <c r="B183" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>153</v>
+      </c>
+      <c r="B184" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>59</v>
+      </c>
+      <c r="B185" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>85</v>
+      </c>
+      <c r="B186" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>149</v>
+      </c>
+      <c r="B187" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>63</v>
+      </c>
+      <c r="B188" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>163</v>
+      </c>
+      <c r="B189" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>142</v>
+      </c>
+      <c r="B190" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>178</v>
+      </c>
+      <c r="B191" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>61</v>
+      </c>
+      <c r="B192" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>39</v>
+      </c>
+      <c r="B193" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>137</v>
+      </c>
+      <c r="B194" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>75</v>
+      </c>
+      <c r="B195" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>95</v>
+      </c>
+      <c r="B196" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>179</v>
+      </c>
+      <c r="B197" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>177</v>
+      </c>
+      <c r="B198" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>25</v>
+      </c>
+      <c r="B199" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>25</v>
+      </c>
+      <c r="B200" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>72</v>
+      </c>
+      <c r="B201" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>156</v>
+      </c>
+      <c r="B202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>88</v>
+      </c>
+      <c r="B203" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>81</v>
+      </c>
+      <c r="B204" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B1" xr:uid="{7FBDDDA3-EEF5-4226-BC33-FF54A0B53D64}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B204">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Emisores.xlsx
+++ b/Emisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb5bc0792163cb23/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{BD17EAFF-BE0D-4454-A41D-9BE3111DDD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D261D2D-B2A9-49DC-AFB2-C194E1FE11B4}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{BD17EAFF-BE0D-4454-A41D-9BE3111DDD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6547DD54-97B1-4286-A6FC-38C260AD16D5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8DC596D6-89CA-4DB4-A49E-B2DC92DCB696}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$193</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="193">
   <si>
     <t>CORPORACION PRIMAX S.A.</t>
   </si>
@@ -608,61 +608,19 @@
     <t>TIPO_DE_INSTRUMENTO</t>
   </si>
   <si>
-    <t>Bonos Empresas Privadas</t>
-  </si>
-  <si>
-    <t>Papeles Comerciales</t>
-  </si>
-  <si>
-    <t>Otros Bonos Sistema Financiero</t>
-  </si>
-  <si>
-    <t>Fondos de Inversion Tradicional Local</t>
-  </si>
-  <si>
-    <t>Depositos a Plazo</t>
-  </si>
-  <si>
-    <t>CD Seriados Subastado Bcos</t>
-  </si>
-  <si>
-    <t>Bonos Gobierno Central de la Republica</t>
-  </si>
-  <si>
-    <t>Tit Deu Emi Estados Extrajero</t>
-  </si>
-  <si>
-    <t>Bonos Subordinados</t>
-  </si>
-  <si>
-    <t>Titulos con Derecho Crediticio</t>
-  </si>
-  <si>
-    <t>Acciones del Capital Social</t>
-  </si>
-  <si>
-    <t>Acciones del Trabajo</t>
-  </si>
-  <si>
-    <t>VRA Empresas Nacionales</t>
-  </si>
-  <si>
-    <t>Fondos Mutuos del Extranjero</t>
-  </si>
-  <si>
-    <t>Tit Deu Emi Empresas Publicas Extranjero</t>
-  </si>
-  <si>
-    <t>Overnight Deposits</t>
-  </si>
-  <si>
-    <t>Fondos de Inversion Alternativos Locales</t>
-  </si>
-  <si>
-    <t>Fondo Mutuos Alterniativos Extranjero</t>
-  </si>
-  <si>
-    <t>Acciones en el Extranjero</t>
+    <t>Renta Variable</t>
+  </si>
+  <si>
+    <t>Renta Fija</t>
+  </si>
+  <si>
+    <t>Alternativos</t>
+  </si>
+  <si>
+    <t>Fondos</t>
+  </si>
+  <si>
+    <t>Davivank SA</t>
   </si>
 </sst>
 </file>
@@ -1060,10 +1018,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBDDDA3-EEF5-4226-BC33-FF54A0B53D64}">
-  <dimension ref="A1:B204"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="2" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1079,7 +1038,7 @@
         <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1087,7 +1046,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1095,7 +1054,7 @@
         <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1103,7 +1062,7 @@
         <v>120</v>
       </c>
       <c r="B5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1111,7 +1070,7 @@
         <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1119,7 +1078,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1127,7 +1086,7 @@
         <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1135,7 +1094,7 @@
         <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1143,7 +1102,7 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1151,7 +1110,7 @@
         <v>158</v>
       </c>
       <c r="B11" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1159,7 +1118,7 @@
         <v>171</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1167,7 +1126,7 @@
         <v>154</v>
       </c>
       <c r="B13" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1175,7 +1134,7 @@
         <v>138</v>
       </c>
       <c r="B14" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1183,7 +1142,7 @@
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1191,7 +1150,7 @@
         <v>169</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1199,7 +1158,7 @@
         <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1207,7 +1166,7 @@
         <v>155</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1215,7 +1174,7 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1223,164 +1182,164 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="B38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
         <v>191</v>
@@ -1388,119 +1347,119 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="B45" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B46" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="B48" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>165</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B53" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s">
         <v>188</v>
@@ -1508,167 +1467,167 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B56" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="B61" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="B63" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="B64" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="B68" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="B69" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="B70" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="B71" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="B72" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="B74" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B76" t="s">
         <v>188</v>
@@ -1676,407 +1635,407 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="B79" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B80" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B82" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="B84" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B85" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B86" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="B88" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="B89" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B90" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>167</v>
+        <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B95" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="B96" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="B97" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="B100" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>58</v>
+        <v>157</v>
       </c>
       <c r="B101" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B103" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B104" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="B105" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="B107" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="B108" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="B109" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B112" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="B113" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="B114" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="B115" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="B116" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B117" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="B118" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B119" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="B120" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="B122" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B123" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="B124" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B125" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="B127" t="s">
         <v>188</v>
@@ -2084,71 +2043,71 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="B128" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B129" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="B130" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="B131" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B133" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B134" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="B135" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B136" t="s">
         <v>188</v>
@@ -2156,551 +2115,463 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="B137" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="B138" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B139" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B140" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B141" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="B142" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>161</v>
+        <v>26</v>
       </c>
       <c r="B143" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="B144" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B145" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="B146" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="B147" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="B148" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B149" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="B150" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="B151" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="B152" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="B154" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B155" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B156" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="B157" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>176</v>
+        <v>37</v>
       </c>
       <c r="B158" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="B159" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="B160" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>143</v>
+        <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="B162" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="B163" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="B164" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="B165" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="B166" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B167" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B168" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="B169" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="B170" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B171" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="B172" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B173" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="B174" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="B175" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B176" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="B177" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="B178" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="B180" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B181" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="B182" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B183" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="B184" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="B185" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="B186" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="B187" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="B188" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="B189" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="B190" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="B191" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B192" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>137</v>
-      </c>
-      <c r="B194" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>75</v>
-      </c>
-      <c r="B195" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>95</v>
-      </c>
-      <c r="B196" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>179</v>
-      </c>
-      <c r="B197" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>177</v>
-      </c>
-      <c r="B198" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>25</v>
-      </c>
-      <c r="B199" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>25</v>
-      </c>
-      <c r="B200" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>72</v>
-      </c>
-      <c r="B201" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>156</v>
-      </c>
-      <c r="B202" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>88</v>
-      </c>
-      <c r="B203" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>81</v>
-      </c>
-      <c r="B204" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{7FBDDDA3-EEF5-4226-BC33-FF54A0B53D64}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B204">
+  <autoFilter ref="A1:B193" xr:uid="{7FBDDDA3-EEF5-4226-BC33-FF54A0B53D64}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B192">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>

--- a/Emisores.xlsx
+++ b/Emisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb5bc0792163cb23/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{BD17EAFF-BE0D-4454-A41D-9BE3111DDD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6547DD54-97B1-4286-A6FC-38C260AD16D5}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{BD17EAFF-BE0D-4454-A41D-9BE3111DDD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84F8A9E3-79C7-436F-AEFB-8F44ADF5C241}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8DC596D6-89CA-4DB4-A49E-B2DC92DCB696}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$190</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="226">
   <si>
     <t>CORPORACION PRIMAX S.A.</t>
   </si>
@@ -428,9 +428,6 @@
     <t>GAS NATURAL DE LIMA Y CALLAO S.A.</t>
   </si>
   <si>
-    <t>FALABELLA PERU S.A.A. (HOLDING)</t>
-  </si>
-  <si>
     <t>ADMINISTRADORA JOCKEY PLAZA SHOPPING CENTER SA</t>
   </si>
   <si>
@@ -621,6 +618,108 @@
   </si>
   <si>
     <t>Davivank SA</t>
+  </si>
+  <si>
+    <t>FALABELLA PERU S.A.A.</t>
+  </si>
+  <si>
+    <t>AMERICA MOVILES SAB DE CV</t>
+  </si>
+  <si>
+    <t>BANCO BRADESCO S.A.</t>
+  </si>
+  <si>
+    <t>BANCO DAVIVIENDA S.A.</t>
+  </si>
+  <si>
+    <t>Banco de Crédito e Inversiones</t>
+  </si>
+  <si>
+    <t>BANCO FALABELLA</t>
+  </si>
+  <si>
+    <t>Banco ICBC</t>
+  </si>
+  <si>
+    <t>Banco Itaú chile</t>
+  </si>
+  <si>
+    <t>Banco Pichincha</t>
+  </si>
+  <si>
+    <t>BANCO SANTANDER MEXICO S.A.</t>
+  </si>
+  <si>
+    <t>BANCO SCOTIABANK DEL PERU S.A.A</t>
+  </si>
+  <si>
+    <t>Banco Scotiabank México</t>
+  </si>
+  <si>
+    <t>BANCOLOMBIA S.A.</t>
+  </si>
+  <si>
+    <t>BARCLAYS BANK PLC</t>
+  </si>
+  <si>
+    <t>BBVA México</t>
+  </si>
+  <si>
+    <t>BROWN BROTHERS HARRIMAN &amp; CO.</t>
+  </si>
+  <si>
+    <t>CITIBANK DEL PERÚ S.A.</t>
+  </si>
+  <si>
+    <t>CITIBANK, N.A.</t>
+  </si>
+  <si>
+    <t>DEUTSCHE BANK AG</t>
+  </si>
+  <si>
+    <t>FINANCIERA CONFIANZA</t>
+  </si>
+  <si>
+    <t>FINANCIERA EFECTIVA S.A.</t>
+  </si>
+  <si>
+    <t>GOBIERNO DE ESTADOS UNIDOS</t>
+  </si>
+  <si>
+    <t>GRUPO NUTRESA S.A.</t>
+  </si>
+  <si>
+    <t>HSBC BANK PLC</t>
+  </si>
+  <si>
+    <t>INRETAIL PHARMA S.A.</t>
+  </si>
+  <si>
+    <t>ITAÚ UNIBANCO S.A.</t>
+  </si>
+  <si>
+    <t>NEXA RESOURCES S.A. (LImite del Exterior)</t>
+  </si>
+  <si>
+    <t>PERU LNG</t>
+  </si>
+  <si>
+    <t>REPUBLICA DE CHILE</t>
+  </si>
+  <si>
+    <t>Scotiabank Chile</t>
+  </si>
+  <si>
+    <t>Scotiabank Colpatria</t>
+  </si>
+  <si>
+    <t>Suzano Austria GmbH</t>
+  </si>
+  <si>
+    <t>THE BANK OF NEW YORK MELLON</t>
+  </si>
+  <si>
+    <t>WELLS FARGO BANK NA</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBDDDA3-EEF5-4226-BC33-FF54A0B53D64}">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B225"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -1027,10 +1126,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1038,7 +1137,7 @@
         <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1046,15 +1145,15 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1062,7 +1161,7 @@
         <v>120</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1070,7 +1169,7 @@
         <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1078,7 +1177,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1086,7 +1185,7 @@
         <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1094,20 +1193,20 @@
         <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>193</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
         <v>190</v>
@@ -1115,247 +1214,247 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="B15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="B20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>197</v>
       </c>
       <c r="B29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="B31" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>184</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="B40" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s">
         <v>188</v>
@@ -1363,111 +1462,111 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="B52" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B53" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
         <v>190</v>
@@ -1475,55 +1574,55 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="B57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="B58" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="B59" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>208</v>
       </c>
       <c r="B61" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="B62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="B63" t="s">
         <v>189</v>
@@ -1531,7 +1630,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="B64" t="s">
         <v>188</v>
@@ -1539,23 +1638,23 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="B66" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="B67" t="s">
         <v>190</v>
@@ -1563,23 +1662,23 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="B70" t="s">
         <v>189</v>
@@ -1587,55 +1686,55 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="B71" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B73" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="B74" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>3</v>
+        <v>191</v>
       </c>
       <c r="B75" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B76" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="B77" t="s">
         <v>190</v>
@@ -1643,15 +1742,15 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="B78" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="B79" t="s">
         <v>190</v>
@@ -1659,55 +1758,55 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="B80" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B83" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="B86" t="s">
         <v>189</v>
@@ -1715,71 +1814,71 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="B88" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>58</v>
+        <v>192</v>
       </c>
       <c r="B89" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B90" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="B91" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="B92" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="B93" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="B95" t="s">
         <v>190</v>
@@ -1787,23 +1886,23 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>170</v>
+        <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="B97" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="B98" t="s">
         <v>189</v>
@@ -1811,15 +1910,15 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="B99" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="B100" t="s">
         <v>189</v>
@@ -1827,15 +1926,15 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="B102" t="s">
         <v>190</v>
@@ -1843,231 +1942,231 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="B103" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="B104" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="B105" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>93</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B109" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="B110" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="B111" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B112" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="B113" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>98</v>
+        <v>215</v>
       </c>
       <c r="B114" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="B115" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="B116" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="B118" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="B119" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="B120" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="B121" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="B122" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="B123" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>22</v>
+        <v>216</v>
       </c>
       <c r="B124" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="B125" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B126" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>52</v>
+        <v>180</v>
       </c>
       <c r="B127" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B128" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="B129" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B130" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="B131" t="s">
         <v>190</v>
@@ -2075,7 +2174,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="B132" t="s">
         <v>190</v>
@@ -2083,15 +2182,15 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="B134" t="s">
         <v>190</v>
@@ -2099,79 +2198,79 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="B135" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="B136" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="B137" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B138" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="B139" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B140" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B141" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="B142" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="B143" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="B144" t="s">
         <v>189</v>
@@ -2179,15 +2278,15 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="B145" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="B146" t="s">
         <v>190</v>
@@ -2195,7 +2294,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>185</v>
+        <v>121</v>
       </c>
       <c r="B147" t="s">
         <v>190</v>
@@ -2203,15 +2302,15 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B148" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="B149" t="s">
         <v>190</v>
@@ -2219,39 +2318,39 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="B150" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B151" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="B152" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="B153" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="B154" t="s">
         <v>190</v>
@@ -2259,23 +2358,23 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B155" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="B156" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="B157" t="s">
         <v>189</v>
@@ -2283,15 +2382,15 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="B158" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="B159" t="s">
         <v>189</v>
@@ -2299,71 +2398,71 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="B160" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B161" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="B162" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="B163" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B164" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="B165" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="B166" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="B167" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="B168" t="s">
         <v>189</v>
@@ -2371,23 +2470,23 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="B169" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="B170" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="B171" t="s">
         <v>188</v>
@@ -2395,47 +2494,47 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B172" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="B173" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="B174" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="B175" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="B176" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="B177" t="s">
         <v>190</v>
@@ -2443,7 +2542,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B178" t="s">
         <v>190</v>
@@ -2451,7 +2550,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="B179" t="s">
         <v>190</v>
@@ -2459,71 +2558,71 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="B180" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>39</v>
+        <v>174</v>
       </c>
       <c r="B181" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>137</v>
+        <v>24</v>
       </c>
       <c r="B182" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="B183" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="B184" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="B185" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="B186" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B188" t="s">
         <v>188</v>
@@ -2531,48 +2630,304 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>192</v>
+        <v>29</v>
       </c>
       <c r="B193" t="s">
-        <v>189</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>89</v>
+      </c>
+      <c r="B194" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>11</v>
+      </c>
+      <c r="B195" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>1</v>
+      </c>
+      <c r="B196" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>107</v>
+      </c>
+      <c r="B197" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>64</v>
+      </c>
+      <c r="B198" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>221</v>
+      </c>
+      <c r="B199" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>222</v>
+      </c>
+      <c r="B200" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>44</v>
+      </c>
+      <c r="B201" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>152</v>
+      </c>
+      <c r="B202" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>59</v>
+      </c>
+      <c r="B203" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>85</v>
+      </c>
+      <c r="B204" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>148</v>
+      </c>
+      <c r="B205" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>223</v>
+      </c>
+      <c r="B206" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>224</v>
+      </c>
+      <c r="B207" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>63</v>
+      </c>
+      <c r="B208" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>162</v>
+      </c>
+      <c r="B209" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>141</v>
+      </c>
+      <c r="B210" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>177</v>
+      </c>
+      <c r="B211" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>61</v>
+      </c>
+      <c r="B212" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>39</v>
+      </c>
+      <c r="B213" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>136</v>
+      </c>
+      <c r="B214" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>75</v>
+      </c>
+      <c r="B215" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>95</v>
+      </c>
+      <c r="B216" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>178</v>
+      </c>
+      <c r="B217" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>176</v>
+      </c>
+      <c r="B218" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>25</v>
+      </c>
+      <c r="B219" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>25</v>
+      </c>
+      <c r="B220" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>72</v>
+      </c>
+      <c r="B221" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>155</v>
+      </c>
+      <c r="B222" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>88</v>
+      </c>
+      <c r="B223" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>225</v>
+      </c>
+      <c r="B224" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>81</v>
+      </c>
+      <c r="B225" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B193" xr:uid="{7FBDDDA3-EEF5-4226-BC33-FF54A0B53D64}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B192">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="A1:B225" xr:uid="{7FBDDDA3-EEF5-4226-BC33-FF54A0B53D64}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B225">
+      <sortCondition ref="A1:A225"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Emisores.xlsx
+++ b/Emisores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb5bc0792163cb23/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{BD17EAFF-BE0D-4454-A41D-9BE3111DDD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84F8A9E3-79C7-436F-AEFB-8F44ADF5C241}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{BD17EAFF-BE0D-4454-A41D-9BE3111DDD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4322711F-F3E2-416D-ACAA-B7AE2AC22AFA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8DC596D6-89CA-4DB4-A49E-B2DC92DCB696}"/>
   </bookViews>
@@ -599,12 +599,6 @@
     <t>Partners Group Cayman Management Direct Infra IV Limited</t>
   </si>
   <si>
-    <t>EMISOR</t>
-  </si>
-  <si>
-    <t>TIPO_DE_INSTRUMENTO</t>
-  </si>
-  <si>
     <t>Renta Variable</t>
   </si>
   <si>
@@ -720,6 +714,12 @@
   </si>
   <si>
     <t>WELLS FARGO BANK NA</t>
+  </si>
+  <si>
+    <t>Emisores</t>
+  </si>
+  <si>
+    <t>Producto</t>
   </si>
 </sst>
 </file>
@@ -778,11 +778,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1125,11 +1126,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>185</v>
+      <c r="A1" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1137,7 +1138,7 @@
         <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1145,7 +1146,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1153,7 +1154,7 @@
         <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1161,7 +1162,7 @@
         <v>120</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1169,7 +1170,7 @@
         <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1177,7 +1178,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1185,7 +1186,7 @@
         <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1193,15 +1194,15 @@
         <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1209,7 +1210,7 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1217,7 +1218,7 @@
         <v>157</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1225,7 +1226,7 @@
         <v>170</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1233,7 +1234,7 @@
         <v>153</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1241,7 +1242,7 @@
         <v>137</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1249,7 +1250,7 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1257,7 +1258,7 @@
         <v>168</v>
       </c>
       <c r="B17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1265,7 +1266,7 @@
         <v>168</v>
       </c>
       <c r="B18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1273,7 +1274,7 @@
         <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1281,7 +1282,7 @@
         <v>154</v>
       </c>
       <c r="B20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1289,7 +1290,7 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1297,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1305,23 +1306,23 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1329,15 +1330,15 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1345,15 +1346,15 @@
         <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1361,15 +1362,15 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1377,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1385,15 +1386,15 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1401,15 +1402,15 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1417,15 +1418,15 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1433,39 +1434,39 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1473,15 +1474,15 @@
         <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B45" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1489,7 +1490,7 @@
         <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1497,7 +1498,7 @@
         <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1505,7 +1506,7 @@
         <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1513,7 +1514,7 @@
         <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1521,7 +1522,7 @@
         <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1529,15 +1530,15 @@
         <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B52" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1545,7 +1546,7 @@
         <v>158</v>
       </c>
       <c r="B53" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1553,7 +1554,7 @@
         <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1561,7 +1562,7 @@
         <v>183</v>
       </c>
       <c r="B55" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1569,7 +1570,7 @@
         <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1577,7 +1578,7 @@
         <v>117</v>
       </c>
       <c r="B57" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1585,7 +1586,7 @@
         <v>43</v>
       </c>
       <c r="B58" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1593,7 +1594,7 @@
         <v>147</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1601,23 +1602,23 @@
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B61" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -1625,7 +1626,7 @@
         <v>145</v>
       </c>
       <c r="B63" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -1633,7 +1634,7 @@
         <v>167</v>
       </c>
       <c r="B64" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -1641,7 +1642,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -1649,7 +1650,7 @@
         <v>110</v>
       </c>
       <c r="B66" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -1657,7 +1658,7 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -1665,7 +1666,7 @@
         <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -1673,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -1681,7 +1682,7 @@
         <v>164</v>
       </c>
       <c r="B70" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -1689,7 +1690,7 @@
         <v>172</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -1697,7 +1698,7 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -1705,7 +1706,7 @@
         <v>50</v>
       </c>
       <c r="B73" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -1713,15 +1714,15 @@
         <v>144</v>
       </c>
       <c r="B74" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B75" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -1729,7 +1730,7 @@
         <v>96</v>
       </c>
       <c r="B76" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -1737,15 +1738,15 @@
         <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B78" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -1753,7 +1754,7 @@
         <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -1761,7 +1762,7 @@
         <v>122</v>
       </c>
       <c r="B80" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -1769,7 +1770,7 @@
         <v>103</v>
       </c>
       <c r="B81" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -1777,7 +1778,7 @@
         <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -1785,7 +1786,7 @@
         <v>123</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -1793,7 +1794,7 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -1801,7 +1802,7 @@
         <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -1809,7 +1810,7 @@
         <v>146</v>
       </c>
       <c r="B86" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -1817,7 +1818,7 @@
         <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -1825,15 +1826,15 @@
         <v>173</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -1841,7 +1842,7 @@
         <v>46</v>
       </c>
       <c r="B90" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1849,23 +1850,23 @@
         <v>131</v>
       </c>
       <c r="B91" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B92" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -1873,7 +1874,7 @@
         <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -1881,7 +1882,7 @@
         <v>90</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -1889,7 +1890,7 @@
         <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -1897,7 +1898,7 @@
         <v>47</v>
       </c>
       <c r="B97" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -1905,7 +1906,7 @@
         <v>161</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -1913,7 +1914,7 @@
         <v>77</v>
       </c>
       <c r="B99" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -1921,7 +1922,7 @@
         <v>139</v>
       </c>
       <c r="B100" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -1929,7 +1930,7 @@
         <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -1937,7 +1938,7 @@
         <v>84</v>
       </c>
       <c r="B102" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -1945,7 +1946,7 @@
         <v>67</v>
       </c>
       <c r="B103" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -1953,7 +1954,7 @@
         <v>127</v>
       </c>
       <c r="B104" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -1961,7 +1962,7 @@
         <v>134</v>
       </c>
       <c r="B105" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -1969,15 +1970,15 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -1985,7 +1986,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -1993,15 +1994,15 @@
         <v>91</v>
       </c>
       <c r="B109" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B110" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2009,7 +2010,7 @@
         <v>149</v>
       </c>
       <c r="B111" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -2017,7 +2018,7 @@
         <v>58</v>
       </c>
       <c r="B112" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -2025,15 +2026,15 @@
         <v>54</v>
       </c>
       <c r="B113" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B114" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -2041,7 +2042,7 @@
         <v>55</v>
       </c>
       <c r="B115" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -2049,7 +2050,7 @@
         <v>31</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -2057,7 +2058,7 @@
         <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -2065,7 +2066,7 @@
         <v>34</v>
       </c>
       <c r="B118" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -2073,7 +2074,7 @@
         <v>159</v>
       </c>
       <c r="B119" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -2081,7 +2082,7 @@
         <v>169</v>
       </c>
       <c r="B120" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -2089,7 +2090,7 @@
         <v>179</v>
       </c>
       <c r="B121" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -2097,7 +2098,7 @@
         <v>36</v>
       </c>
       <c r="B122" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -2105,15 +2106,15 @@
         <v>45</v>
       </c>
       <c r="B123" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -2121,7 +2122,7 @@
         <v>35</v>
       </c>
       <c r="B125" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -2129,7 +2130,7 @@
         <v>156</v>
       </c>
       <c r="B126" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -2137,7 +2138,7 @@
         <v>180</v>
       </c>
       <c r="B127" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -2145,7 +2146,7 @@
         <v>38</v>
       </c>
       <c r="B128" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -2153,7 +2154,7 @@
         <v>20</v>
       </c>
       <c r="B129" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -2161,7 +2162,7 @@
         <v>49</v>
       </c>
       <c r="B130" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -2169,7 +2170,7 @@
         <v>106</v>
       </c>
       <c r="B131" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -2177,7 +2178,7 @@
         <v>93</v>
       </c>
       <c r="B132" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -2185,7 +2186,7 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -2193,15 +2194,15 @@
         <v>66</v>
       </c>
       <c r="B134" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B135" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -2209,7 +2210,7 @@
         <v>108</v>
       </c>
       <c r="B136" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -2217,7 +2218,7 @@
         <v>112</v>
       </c>
       <c r="B137" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -2225,7 +2226,7 @@
         <v>62</v>
       </c>
       <c r="B138" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -2233,7 +2234,7 @@
         <v>116</v>
       </c>
       <c r="B139" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -2241,7 +2242,7 @@
         <v>98</v>
       </c>
       <c r="B140" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -2249,7 +2250,7 @@
         <v>126</v>
       </c>
       <c r="B141" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -2257,7 +2258,7 @@
         <v>171</v>
       </c>
       <c r="B142" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -2265,7 +2266,7 @@
         <v>100</v>
       </c>
       <c r="B143" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -2273,7 +2274,7 @@
         <v>130</v>
       </c>
       <c r="B144" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -2281,7 +2282,7 @@
         <v>104</v>
       </c>
       <c r="B145" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -2289,7 +2290,7 @@
         <v>97</v>
       </c>
       <c r="B146" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -2297,7 +2298,7 @@
         <v>121</v>
       </c>
       <c r="B147" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -2305,7 +2306,7 @@
         <v>140</v>
       </c>
       <c r="B148" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -2313,7 +2314,7 @@
         <v>115</v>
       </c>
       <c r="B149" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -2321,7 +2322,7 @@
         <v>22</v>
       </c>
       <c r="B150" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -2329,7 +2330,7 @@
         <v>99</v>
       </c>
       <c r="B151" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -2337,7 +2338,7 @@
         <v>132</v>
       </c>
       <c r="B152" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -2345,7 +2346,7 @@
         <v>52</v>
       </c>
       <c r="B153" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -2353,7 +2354,7 @@
         <v>102</v>
       </c>
       <c r="B154" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -2361,7 +2362,7 @@
         <v>74</v>
       </c>
       <c r="B155" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -2369,7 +2370,7 @@
         <v>160</v>
       </c>
       <c r="B156" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -2377,7 +2378,7 @@
         <v>138</v>
       </c>
       <c r="B157" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -2385,7 +2386,7 @@
         <v>109</v>
       </c>
       <c r="B158" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -2393,7 +2394,7 @@
         <v>143</v>
       </c>
       <c r="B159" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -2401,7 +2402,7 @@
         <v>79</v>
       </c>
       <c r="B160" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -2409,15 +2410,15 @@
         <v>48</v>
       </c>
       <c r="B161" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B162" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -2425,7 +2426,7 @@
         <v>56</v>
       </c>
       <c r="B163" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -2433,7 +2434,7 @@
         <v>114</v>
       </c>
       <c r="B164" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -2441,7 +2442,7 @@
         <v>82</v>
       </c>
       <c r="B165" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -2449,7 +2450,7 @@
         <v>30</v>
       </c>
       <c r="B166" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -2457,7 +2458,7 @@
         <v>113</v>
       </c>
       <c r="B167" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -2465,7 +2466,7 @@
         <v>150</v>
       </c>
       <c r="B168" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -2473,7 +2474,7 @@
         <v>26</v>
       </c>
       <c r="B169" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -2481,7 +2482,7 @@
         <v>21</v>
       </c>
       <c r="B170" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -2489,7 +2490,7 @@
         <v>129</v>
       </c>
       <c r="B171" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -2497,7 +2498,7 @@
         <v>175</v>
       </c>
       <c r="B172" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -2505,7 +2506,7 @@
         <v>184</v>
       </c>
       <c r="B173" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -2513,15 +2514,15 @@
         <v>163</v>
       </c>
       <c r="B174" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B175" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -2529,7 +2530,7 @@
         <v>142</v>
       </c>
       <c r="B176" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -2537,7 +2538,7 @@
         <v>78</v>
       </c>
       <c r="B177" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -2545,7 +2546,7 @@
         <v>119</v>
       </c>
       <c r="B178" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -2553,7 +2554,7 @@
         <v>92</v>
       </c>
       <c r="B179" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -2561,7 +2562,7 @@
         <v>151</v>
       </c>
       <c r="B180" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -2569,7 +2570,7 @@
         <v>174</v>
       </c>
       <c r="B181" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -2577,7 +2578,7 @@
         <v>24</v>
       </c>
       <c r="B182" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -2585,7 +2586,7 @@
         <v>24</v>
       </c>
       <c r="B183" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -2593,7 +2594,7 @@
         <v>27</v>
       </c>
       <c r="B184" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -2601,15 +2602,15 @@
         <v>37</v>
       </c>
       <c r="B185" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B186" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -2617,7 +2618,7 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -2625,7 +2626,7 @@
         <v>18</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -2633,7 +2634,7 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -2641,7 +2642,7 @@
         <v>181</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -2649,7 +2650,7 @@
         <v>83</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -2657,7 +2658,7 @@
         <v>124</v>
       </c>
       <c r="B192" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -2665,7 +2666,7 @@
         <v>29</v>
       </c>
       <c r="B193" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -2673,7 +2674,7 @@
         <v>89</v>
       </c>
       <c r="B194" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -2681,7 +2682,7 @@
         <v>11</v>
       </c>
       <c r="B195" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -2689,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="B196" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -2697,7 +2698,7 @@
         <v>107</v>
       </c>
       <c r="B197" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -2705,23 +2706,23 @@
         <v>64</v>
       </c>
       <c r="B198" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B199" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B200" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -2729,7 +2730,7 @@
         <v>44</v>
       </c>
       <c r="B201" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -2737,7 +2738,7 @@
         <v>152</v>
       </c>
       <c r="B202" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -2745,7 +2746,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -2753,7 +2754,7 @@
         <v>85</v>
       </c>
       <c r="B204" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -2761,23 +2762,23 @@
         <v>148</v>
       </c>
       <c r="B205" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B206" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B207" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -2785,7 +2786,7 @@
         <v>63</v>
       </c>
       <c r="B208" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -2793,7 +2794,7 @@
         <v>162</v>
       </c>
       <c r="B209" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -2801,7 +2802,7 @@
         <v>141</v>
       </c>
       <c r="B210" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -2809,7 +2810,7 @@
         <v>177</v>
       </c>
       <c r="B211" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -2817,7 +2818,7 @@
         <v>61</v>
       </c>
       <c r="B212" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -2825,7 +2826,7 @@
         <v>39</v>
       </c>
       <c r="B213" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -2833,7 +2834,7 @@
         <v>136</v>
       </c>
       <c r="B214" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -2841,7 +2842,7 @@
         <v>75</v>
       </c>
       <c r="B215" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -2849,7 +2850,7 @@
         <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -2857,7 +2858,7 @@
         <v>178</v>
       </c>
       <c r="B217" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -2865,7 +2866,7 @@
         <v>176</v>
       </c>
       <c r="B218" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -2873,7 +2874,7 @@
         <v>25</v>
       </c>
       <c r="B219" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -2881,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="B220" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -2889,7 +2890,7 @@
         <v>72</v>
       </c>
       <c r="B221" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -2897,7 +2898,7 @@
         <v>155</v>
       </c>
       <c r="B222" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -2905,15 +2906,15 @@
         <v>88</v>
       </c>
       <c r="B223" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -2921,7 +2922,7 @@
         <v>81</v>
       </c>
       <c r="B225" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
